--- a/Pruebas calificadas/COLEGIO-ARGELIA-(IED)-501_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-ARGELIA-(IED)-501_CALIFICADO.xlsx
@@ -2313,10 +2313,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3321,10 +3325,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3570,10 +3578,14 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3819,10 +3831,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4068,10 +4084,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -4317,10 +4337,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4819,10 +4843,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -5574,10 +5602,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -6329,10 +6361,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -6578,10 +6614,14 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -11618,10 +11658,14 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -12622,10 +12666,14 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -12871,10 +12919,14 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -13120,10 +13172,14 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -13369,10 +13425,14 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -13618,10 +13678,14 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -14120,10 +14184,14 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -14875,10 +14943,14 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -15630,10 +15702,14 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -15879,10 +15955,14 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>111001100084</t>
+          <t>111001100064</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-ARGELIA-(IED)-501_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-ARGELIA-(IED)-501_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15959,7 +15959,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17730,7 +17730,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18236,7 +18236,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18489,7 +18489,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-ARGELIA-(IED)-501_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-ARGELIA-(IED)-501_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1807,11 +1791,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -1819,7 +1799,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2060,11 +2040,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -2072,7 +2048,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2313,11 +2289,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -2325,7 +2297,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2566,11 +2538,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -2578,7 +2546,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2819,11 +2787,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -2831,7 +2795,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3072,11 +3036,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -3084,7 +3044,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3325,11 +3285,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -3337,7 +3293,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3578,11 +3534,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -3590,7 +3542,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3831,11 +3783,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -3843,7 +3791,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4084,11 +4032,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -4096,7 +4040,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4337,11 +4281,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -4349,7 +4289,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4590,11 +4530,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -4602,7 +4538,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4843,11 +4779,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -4855,7 +4787,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5096,11 +5028,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -5108,7 +5036,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5349,11 +5277,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -5361,7 +5285,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5602,11 +5526,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -5614,7 +5534,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5855,11 +5775,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -5867,7 +5783,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6108,11 +6024,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -6120,7 +6032,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6361,11 +6273,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -6373,7 +6281,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6614,11 +6522,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -6626,7 +6530,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6867,11 +6771,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -6879,7 +6779,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7120,11 +7020,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -7132,7 +7028,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7373,11 +7269,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -7385,7 +7277,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7626,11 +7518,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -7638,7 +7526,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7863,11 +7751,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -7875,7 +7759,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8116,11 +8000,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -8128,7 +8008,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8369,11 +8249,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -8381,7 +8257,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8622,11 +8498,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -8634,7 +8506,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8875,11 +8747,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -8887,7 +8755,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9128,11 +8996,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -9140,7 +9004,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9381,11 +9245,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -9393,7 +9253,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9634,11 +9494,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -9646,7 +9502,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9887,11 +9743,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -9899,7 +9751,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10140,11 +9992,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -10152,7 +10000,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10393,11 +10241,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -10405,7 +10249,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10646,11 +10490,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -10658,7 +10498,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10899,11 +10739,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -10911,7 +10747,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11152,11 +10988,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -11164,7 +10996,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11405,11 +11237,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -11417,7 +11245,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11658,11 +11486,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -11670,7 +11494,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11907,11 +11731,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -11919,7 +11739,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12160,11 +11980,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -12172,7 +11988,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12405,11 +12221,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -12417,7 +12229,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12658,11 +12470,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -12670,7 +12478,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12911,11 +12719,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -12923,7 +12727,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13164,11 +12968,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -13176,7 +12976,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13417,11 +13217,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -13429,7 +13225,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13670,11 +13466,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -13682,7 +13474,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13923,11 +13715,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -13935,7 +13723,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14176,11 +13964,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -14188,7 +13972,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14429,11 +14213,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -14441,7 +14221,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14682,11 +14462,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -14694,7 +14470,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14935,11 +14711,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -14947,7 +14719,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15188,11 +14960,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -15200,7 +14968,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15441,11 +15209,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -15453,7 +15217,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15694,11 +15458,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -15706,7 +15466,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15947,11 +15707,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -15959,7 +15715,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16200,11 +15956,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -16212,7 +15964,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16453,11 +16205,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -16465,7 +16213,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16706,11 +16454,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -16718,7 +16462,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16959,11 +16703,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -16971,7 +16711,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17212,11 +16952,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -17224,7 +16960,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17465,11 +17201,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -17477,7 +17209,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17718,11 +17450,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -17730,7 +17458,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17971,11 +17699,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -17983,7 +17707,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18224,11 +17948,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -18236,7 +17956,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18477,11 +18197,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -18489,7 +18205,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18730,11 +18446,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -18742,7 +18454,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18983,11 +18695,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -18995,7 +18703,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19236,11 +18944,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -19248,7 +18952,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
